--- a/docs/test-plan.xlsx
+++ b/docs/test-plan.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6368a6be5aca3f60/Documents/HTL/WMC/room-food/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c_wim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1140" documentId="8_{6403F3F5-45D2-4B19-BA55-5D98014D21A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69EA73EE-84C0-4862-A632-1FF536E20DD2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65A76573-87E4-4F5B-8F3D-BD9BFFB98735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C42BC90F-3C54-42E4-BD98-606C1062A153}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C42BC90F-3C54-42E4-BD98-606C1062A153}"/>
   </bookViews>
   <sheets>
     <sheet name="All Tests" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sprint 2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="274">
   <si>
     <t>Test Plan - Room Food</t>
   </si>
@@ -724,6 +725,150 @@
   </si>
   <si>
     <t>The backend returns the correct meal plan data, which is ready to be displayed, without editing yet</t>
+  </si>
+  <si>
+    <t>Sprint 2 Test Plan</t>
+  </si>
+  <si>
+    <t>TC-21</t>
+  </si>
+  <si>
+    <t>TC-22</t>
+  </si>
+  <si>
+    <t>TC-23</t>
+  </si>
+  <si>
+    <t>TC-24</t>
+  </si>
+  <si>
+    <t>TC-25</t>
+  </si>
+  <si>
+    <t>TC-27</t>
+  </si>
+  <si>
+    <t>TC-26</t>
+  </si>
+  <si>
+    <t>The user has the means to customize their profile. Including, first name, last name, DOB and profile picture.</t>
+  </si>
+  <si>
+    <t>Login and Sign up</t>
+  </si>
+  <si>
+    <t>User has the ability to create an account and/or log into an account</t>
+  </si>
+  <si>
+    <t>Password hashing</t>
+  </si>
+  <si>
+    <t>Adding new properies to user</t>
+  </si>
+  <si>
+    <t>Entered password gets encrypted with the hashing method</t>
+  </si>
+  <si>
+    <t>Adding profile page</t>
+  </si>
+  <si>
+    <t>Password salting</t>
+  </si>
+  <si>
+    <t>Cookies and salting</t>
+  </si>
+  <si>
+    <t>User is able to see all of their correct information on the profile page</t>
+  </si>
+  <si>
+    <t>Able to retrieve the new properties from user data table</t>
+  </si>
+  <si>
+    <t>Logged in user gets a token for the session they are logged in</t>
+  </si>
+  <si>
+    <t>Delete account</t>
+  </si>
+  <si>
+    <t>Log out button</t>
+  </si>
+  <si>
+    <t>When the delete account button is clicked the user's account gets removed everywhere and from the database</t>
+  </si>
+  <si>
+    <t>User session ends</t>
+  </si>
+  <si>
+    <t>Add functionality for editing an existing meal</t>
+  </si>
+  <si>
+    <t>Room backend</t>
+  </si>
+  <si>
+    <t>Create room frontend</t>
+  </si>
+  <si>
+    <t>Edit room frontend</t>
+  </si>
+  <si>
+    <t>Delete room frontend</t>
+  </si>
+  <si>
+    <t>Room overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ability to view all the rooms the user has currently joined. </t>
+  </si>
+  <si>
+    <t>Miscellaneoous</t>
+  </si>
+  <si>
+    <t>Tasks that are not under a categoy</t>
+  </si>
+  <si>
+    <t>User is able to successfully invite another user into their room</t>
+  </si>
+  <si>
+    <t>Control access to pages if not logged in</t>
+  </si>
+  <si>
+    <t>User is able to create a new room</t>
+  </si>
+  <si>
+    <t>User is able to edit the properites of an already created room.</t>
+  </si>
+  <si>
+    <t>User can't access dofferent functionalities unless logged in</t>
+  </si>
+  <si>
+    <t>User is able to delete a created room</t>
+  </si>
+  <si>
+    <t>Add error page</t>
+  </si>
+  <si>
+    <t>Once a meal has been added, user is able to change the properties of that meal</t>
+  </si>
+  <si>
+    <t>When the user messes up something the user gets redirected to an "error page" displaying an error message</t>
+  </si>
+  <si>
+    <t>Able to insert, update and get rooms from room database</t>
+  </si>
+  <si>
+    <t>Paased</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Rooms should include a calendar view for meal plans, an ingredient list, owner controls to edit plans and manage members, and allow users to join multiple rooms with separate meal plans for each.</t>
+  </si>
+  <si>
+    <t>Password gets salted and then hashed</t>
   </si>
 </sst>
 </file>
@@ -765,7 +910,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -781,6 +926,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +1077,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1007,6 +1158,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1022,6 +1189,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1341,9 +1512,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EC47FC-93F6-45F0-B905-DC3135FC4D24}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3295,20 +3463,17 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86054CE-8067-4A68-B442-AE26D5B1146F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
     <col min="3" max="3" width="18.77734375" customWidth="1"/>
     <col min="4" max="4" width="38.77734375" customWidth="1"/>
     <col min="5" max="5" width="6.109375" customWidth="1"/>
@@ -3318,14 +3483,14 @@
     <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="27" t="s">
         <v>156</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
     </row>
-    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
@@ -3354,7 +3519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -3376,14 +3541,14 @@
       <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>15</v>
+      <c r="H5" s="32" t="s">
+        <v>269</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -3400,7 +3565,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -3417,7 +3582,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="17"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3428,7 +3593,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="18"/>
     </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -3450,14 +3615,14 @@
       <c r="G9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>15</v>
+      <c r="H9" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -3474,7 +3639,7 @@
       <c r="H10" s="7"/>
       <c r="I10" s="17"/>
     </row>
-    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -3491,7 +3656,7 @@
       <c r="H11" s="7"/>
       <c r="I11" s="17"/>
     </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3508,7 +3673,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3525,7 +3690,7 @@
       <c r="H13" s="7"/>
       <c r="I13" s="17"/>
     </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3541,8 +3706,9 @@
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3553,7 +3719,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="18"/>
     </row>
-    <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>97</v>
       </c>
@@ -3575,11 +3741,11 @@
       <c r="G16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>15</v>
+      <c r="H16" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -3649,11 +3815,11 @@
       <c r="G20" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>15</v>
+      <c r="H20" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -3740,11 +3906,11 @@
       <c r="G25" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>15</v>
+      <c r="H25" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -3814,11 +3980,11 @@
       <c r="G29" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>15</v>
+      <c r="H29" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -3922,11 +4088,11 @@
       <c r="G35" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>15</v>
+      <c r="H35" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -3996,11 +4162,11 @@
       <c r="G39" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>15</v>
+      <c r="H39" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -4070,11 +4236,11 @@
       <c r="G43" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>15</v>
+      <c r="H43" s="32" t="s">
+        <v>271</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -4127,11 +4293,922 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDF8731F-ABEA-42F1-9688-6D766352E85C}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" customWidth="1"/>
+    <col min="4" max="4" width="38.77734375" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A1" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+    </row>
+    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="5">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="5">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="5">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="25">
+        <v>5</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="25">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="30">
+        <v>2</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="30">
+        <v>3</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="30">
+        <v>4</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="30">
+        <v>5</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="30">
+        <v>6</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="30">
+        <v>7</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20"/>
+    </row>
+    <row r="22" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="25">
+        <v>97</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E22" s="25">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="24"/>
+    </row>
+    <row r="25" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" s="25">
+        <v>17</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" s="25">
+        <v>1</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="5">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="5">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="17"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="24"/>
+    </row>
+    <row r="29" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B29" s="25">
+        <v>18</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="25">
+        <v>1</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="5">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="5">
+        <v>3</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="17"/>
+    </row>
+    <row r="32" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="5">
+        <v>4</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="17"/>
+    </row>
+    <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="5">
+        <v>5</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="17"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B35" s="25">
+        <v>19</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" s="25">
+        <v>1</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="5">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="17"/>
+    </row>
+    <row r="37" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="5">
+        <v>3</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="17"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
+    </row>
+    <row r="39" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="25">
+        <v>21</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="12">
+        <v>1</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="4">
+        <v>2</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="17"/>
+    </row>
+    <row r="41" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="4">
+        <v>3</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="17"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="24"/>
+    </row>
+    <row r="43" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" s="25">
+        <v>21</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E43" s="12">
+        <v>1</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="4">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="H44" s="7"/>
+      <c r="I44" s="17"/>
+    </row>
+    <row r="45" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="4">
+        <v>3</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="17"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="24"/>
+    </row>
+    <row r="47" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="25">
+        <v>21</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" s="12">
+        <v>1</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="4">
+        <v>2</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="H48" s="7"/>
+      <c r="I48" s="17"/>
+    </row>
+    <row r="49" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="4">
+        <v>3</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H49" s="7"/>
+      <c r="I49" s="17"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="68d4fa24-27bc-4a2b-8b10-66e8c88ad728" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4140,7 +5217,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100BB7BF5C2C52F2C4AA8EF209DE34A1A0F" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8842282b29ac7e735b9ed755721e531">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="68d4fa24-27bc-4a2b-8b10-66e8c88ad728" xmlns:ns4="2c986a59-9623-43da-912b-e65b30ca5c76" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc8b420dc9c44da9302fa0caf442eccd" ns3:_="" ns4:_="">
     <xsd:import namespace="68d4fa24-27bc-4a2b-8b10-66e8c88ad728"/>
@@ -4347,15 +5424,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="68d4fa24-27bc-4a2b-8b10-66e8c88ad728" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B4E38F-F5AD-4E98-885A-0062393198BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="2c986a59-9623-43da-912b-e65b30ca5c76"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="68d4fa24-27bc-4a2b-8b10-66e8c88ad728"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C957952-7C1E-4B59-84B8-BFBB782867EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -4363,7 +5449,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F4E4E5-030E-47C8-9711-F045F3C756AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4380,21 +5466,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B4E38F-F5AD-4E98-885A-0062393198BC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="2c986a59-9623-43da-912b-e65b30ca5c76"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="68d4fa24-27bc-4a2b-8b10-66e8c88ad728"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>